--- a/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/feb-2026.xlsx
+++ b/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/feb-2026.xlsx
@@ -565,11 +565,11 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>1369.056</v>
+        <v>63090.6</v>
       </c>
     </row>
     <row r="3">
@@ -626,11 +626,11 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>14.148</v>
+        <v>651.99</v>
       </c>
     </row>
     <row r="4">
@@ -687,11 +687,11 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>769.5</v>
+        <v>35461.09</v>
       </c>
     </row>
     <row r="5">
@@ -748,11 +748,11 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>710.856</v>
+        <v>32758.58</v>
       </c>
     </row>
     <row r="6">
@@ -809,11 +809,11 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>645.0359999999999</v>
+        <v>29725.38</v>
       </c>
     </row>
     <row r="7">
@@ -870,11 +870,11 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>1026.792</v>
+        <v>47317.95</v>
       </c>
     </row>
     <row r="8">
@@ -931,11 +931,11 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>1042.15</v>
+        <v>48025.7</v>
       </c>
     </row>
     <row r="9">
@@ -992,11 +992,11 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>1329.564</v>
+        <v>61270.68</v>
       </c>
     </row>
     <row r="10">
@@ -1053,11 +1053,11 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>1474.368</v>
+        <v>67943.72</v>
       </c>
     </row>
     <row r="11">
@@ -1114,11 +1114,11 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>34.007</v>
+        <v>1567.15</v>
       </c>
     </row>
     <row r="12">
@@ -1175,11 +1175,11 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>829.432</v>
+        <v>38222.95</v>
       </c>
     </row>
     <row r="13">
@@ -1236,11 +1236,11 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>177.714</v>
+        <v>8189.65</v>
       </c>
     </row>
     <row r="14">
@@ -1297,11 +1297,11 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>156.871</v>
+        <v>7229.13</v>
       </c>
     </row>
     <row r="15">
@@ -1358,11 +1358,11 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>378.465</v>
+        <v>17440.91</v>
       </c>
     </row>
     <row r="16">
@@ -1419,11 +1419,11 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>232.564</v>
+        <v>10717.31</v>
       </c>
     </row>
     <row r="17">
@@ -1480,11 +1480,11 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>820.556</v>
+        <v>37813.92</v>
       </c>
     </row>
     <row r="18">
@@ -1541,11 +1541,11 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>27.93</v>
+        <v>1287.11</v>
       </c>
     </row>
     <row r="19">
@@ -1602,11 +1602,11 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>210.624</v>
+        <v>9706.25</v>
       </c>
     </row>
   </sheetData>
